--- a/Working List.xlsx
+++ b/Working List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Repos\mn_data_redesign\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F24174-442B-4ADA-9B33-886F73A44852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C1FDBF-9570-46A7-9FCF-18F850C36B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{8FBAF839-E732-4364-B5DC-26B38382FF1D}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{8FBAF839-E732-4364-B5DC-26B38382FF1D}"/>
   </bookViews>
   <sheets>
     <sheet name="list" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
   <si>
     <t>说明</t>
   </si>
@@ -33,10 +33,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>落表</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>.sql 文件名</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -182,6 +178,21 @@
   </si>
   <si>
     <t>map_pay_stats</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_flagged_d</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ads_cn.ads_user_flagged_i_d</t>
+  </si>
+  <si>
+    <t>OK</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -804,14 +815,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -828,6 +836,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1204,119 +1224,133 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D639A680-3387-4533-8FC5-EB02377F5246}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.88671875" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" customWidth="1"/>
+    <col min="2" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="5" width="8.88671875" style="10"/>
+    <col min="6" max="6" width="26.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="2"/>
+      <c r="D2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="9"/>
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="2"/>
+      <c r="D3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="9"/>
       <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="2"/>
+      <c r="D4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="9"/>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="2"/>
+      <c r="D5" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="9"/>
       <c r="F5" s="1"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="2"/>
+      <c r="D6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="9"/>
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="2"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
       <c r="F7" s="1"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="1"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
       <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1325,85 +1359,65 @@
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
       <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
       <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="2"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
       <c r="F14" s="1"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="2"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
       <c r="F15" s="1"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+      <c r="D16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -1422,22 +1436,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1445,7 +1459,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1453,75 +1467,75 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="S5" s="4"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="S5" s="3"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="S6" s="4"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="S6" s="3"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>21</v>
+      <c r="A8" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>27</v>
+      <c r="A9" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>29</v>
+      <c r="A10" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>28</v>
+      <c r="A11" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>23</v>
+      <c r="A12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1529,7 +1543,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1537,7 +1551,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1545,7 +1559,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1553,15 +1567,15 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>24</v>
+      <c r="A17" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1569,7 +1583,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1577,7 +1591,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1585,7 +1599,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1593,7 +1607,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1601,7 +1615,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>

--- a/Working List.xlsx
+++ b/Working List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Repos\mn_data_redesign\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C1FDBF-9570-46A7-9FCF-18F850C36B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241612F9-5C7A-4974-8859-8568C587CAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{8FBAF839-E732-4364-B5DC-26B38382FF1D}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
   <si>
     <t>说明</t>
   </si>
@@ -165,10 +165,6 @@
     <t>map_ad_stats</t>
   </si>
   <si>
-    <t>user_login_ret</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>map_ret_lt_ltv</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -193,6 +189,10 @@
   </si>
   <si>
     <t>OK</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_ret_lt_ltv</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1230,7 +1230,7 @@
     <col min="1" max="1" width="23.88671875" customWidth="1"/>
     <col min="2" max="3" width="16.44140625" customWidth="1"/>
     <col min="4" max="5" width="8.88671875" style="10"/>
-    <col min="6" max="6" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
@@ -1260,7 +1260,7 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="1"/>
@@ -1272,7 +1272,7 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="1"/>
@@ -1284,7 +1284,7 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="1"/>
@@ -1296,7 +1296,7 @@
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="1"/>
@@ -1308,14 +1308,14 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1335,11 +1335,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="9"/>
+      <c r="D9" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="E9" s="9"/>
       <c r="F9" s="1"/>
     </row>
@@ -1355,7 +1357,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1369,13 +1371,15 @@
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="9"/>
+      <c r="D12" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="E12" s="9"/>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1405,18 +1409,18 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Working List.xlsx
+++ b/Working List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Repos\mn_data_redesign\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241612F9-5C7A-4974-8859-8568C587CAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF404B6-A875-4763-BCC0-34CEDEE84878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{8FBAF839-E732-4364-B5DC-26B38382FF1D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{8FBAF839-E732-4364-B5DC-26B38382FF1D}"/>
   </bookViews>
   <sheets>
     <sheet name="list" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="49">
   <si>
     <t>说明</t>
   </si>
@@ -193,6 +193,13 @@
   </si>
   <si>
     <t>user_ret_lt_ltv</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dim_cn.dim_channel_a_d_cn</t>
+  </si>
+  <si>
+    <t>有现成的</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -556,7 +563,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -686,6 +693,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -815,7 +833,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -848,6 +866,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1224,16 +1245,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D639A680-3387-4533-8FC5-EB02377F5246}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.88671875" customWidth="1"/>
     <col min="2" max="3" width="16.44140625" customWidth="1"/>
     <col min="4" max="5" width="8.88671875" style="10"/>
     <col min="6" max="6" width="27.77734375" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -1253,7 +1275,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
@@ -1265,7 +1287,7 @@
       <c r="E2" s="9"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>32</v>
       </c>
@@ -1274,10 +1296,17 @@
       <c r="D3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E3" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>33</v>
       </c>
@@ -1289,7 +1318,7 @@
       <c r="E4" s="9"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
@@ -1301,7 +1330,7 @@
       <c r="E5" s="9"/>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
@@ -1313,7 +1342,7 @@
       <c r="E6" s="9"/>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
@@ -1323,7 +1352,7 @@
       <c r="E7" s="9"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
@@ -1333,7 +1362,7 @@
       <c r="E8" s="9"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
@@ -1345,7 +1374,7 @@
       <c r="E9" s="9"/>
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
@@ -1355,7 +1384,7 @@
       <c r="E10" s="9"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>41</v>
       </c>
@@ -1365,7 +1394,7 @@
       <c r="E11" s="9"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>38</v>
       </c>
@@ -1377,7 +1406,7 @@
       <c r="E12" s="9"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>39</v>
       </c>
@@ -1387,7 +1416,7 @@
       <c r="E13" s="9"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>29</v>
       </c>
@@ -1397,7 +1426,7 @@
       <c r="E14" s="9"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>36</v>
       </c>
@@ -1407,7 +1436,7 @@
       <c r="E15" s="9"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>43</v>
       </c>

--- a/Working List.xlsx
+++ b/Working List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Repos\mn_data_redesign\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF404B6-A875-4763-BCC0-34CEDEE84878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57D50DF-CAAC-4B85-B1EB-7F8F8A3803BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{8FBAF839-E732-4364-B5DC-26B38382FF1D}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{8FBAF839-E732-4364-B5DC-26B38382FF1D}"/>
   </bookViews>
   <sheets>
     <sheet name="list" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="65">
   <si>
     <t>说明</t>
   </si>
@@ -134,10 +134,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>dim_ad_ad_slot</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>dim_channel</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -154,10 +150,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>ugc_core_stats_d</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>map_game_stats</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -192,14 +184,82 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>user_ret_lt_ltv</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>dim_cn.dim_channel_a_d_cn</t>
   </si>
   <si>
     <t>有现成的</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ugc_core_stats</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>日-异常用户</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>日-地图广告数据</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dim_ad_slot</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>广告位字典</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>渠道字典</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>日-DAU与收入目标</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊地图</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊整合包</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>日-用户地图游戏数据</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>日-用户地图消费数据</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>日-当日登录用户及后续登录与付费</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_login_pay</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dim_cn.dim_ad_slot_config_a_d</t>
+  </si>
+  <si>
+    <t>dim_cn.dim_op_goal_a_d</t>
+  </si>
+  <si>
+    <t>dim_cn.dim_special_contentpack_a_d</t>
+  </si>
+  <si>
+    <t>dim_cn.dim_special_map_a_d</t>
+  </si>
+  <si>
+    <t>验证?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dws_cn.dws_client_game_user_map_stats_i_d</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -563,7 +623,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -693,17 +753,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -833,7 +882,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -866,9 +915,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1249,10 +1295,11 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.88671875" customWidth="1"/>
-    <col min="2" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="5" width="8.88671875" style="10"/>
-    <col min="6" max="6" width="27.77734375" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="2" max="2" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="6" width="8.88671875" style="10"/>
+    <col min="7" max="7" width="41.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1269,152 +1316,206 @@
         <v>4</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="C2" s="1"/>
       <c r="D2" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="D3" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
+      </c>
+      <c r="F3" s="9"/>
+      <c r="G3" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="C4" s="1"/>
       <c r="D4" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="C5" s="1"/>
       <c r="D5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="9"/>
+      <c r="G5" s="1" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="C6" s="1"/>
       <c r="D6" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="9"/>
+      <c r="D7" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="E7" s="9"/>
-      <c r="F7" s="1"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="9"/>
+      <c r="D8" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="E8" s="9"/>
-      <c r="F8" s="1"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="1" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="1"/>
+        <v>38</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C9" s="1"/>
       <c r="D9" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E9" s="9"/>
-      <c r="F9" s="1"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
-      <c r="F10" s="1"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
-      <c r="F11" s="1"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="C12" s="1"/>
       <c r="D12" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E12" s="9"/>
-      <c r="F12" s="1"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
-      <c r="F13" s="1"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1424,37 +1525,43 @@
       <c r="C14" s="1"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
-      <c r="F14" s="1"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="1"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="C16" s="1"/>
       <c r="D16" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Working List.xlsx
+++ b/Working List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Repos\mn_data_redesign\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57D50DF-CAAC-4B85-B1EB-7F8F8A3803BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC3EFC9-4131-4C4D-A2E9-A28AB3183C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{8FBAF839-E732-4364-B5DC-26B38382FF1D}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
   <si>
     <t>说明</t>
   </si>
@@ -882,7 +882,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -914,6 +914,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1475,7 +1478,9 @@
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="9"/>
+      <c r="D10" s="11" t="s">
+        <v>43</v>
+      </c>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="1"/>
@@ -1486,7 +1491,9 @@
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="9"/>
+      <c r="D11" s="11" t="s">
+        <v>43</v>
+      </c>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="1"/>
@@ -1512,7 +1519,9 @@
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="9"/>
+      <c r="D13" s="11" t="s">
+        <v>43</v>
+      </c>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="1"/>
@@ -1523,7 +1532,9 @@
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
-      <c r="D14" s="9"/>
+      <c r="D14" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="1"/>

--- a/Working List.xlsx
+++ b/Working List.xlsx
@@ -8,20 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Repos\mn_data_redesign\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC3EFC9-4131-4C4D-A2E9-A28AB3183C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8247C4B5-D5B9-46EE-BDFF-09758F02D7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{8FBAF839-E732-4364-B5DC-26B38382FF1D}"/>
   </bookViews>
   <sheets>
     <sheet name="list" sheetId="1" r:id="rId1"/>
     <sheet name="ads_ugc_core_metrics_s_d" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="86">
   <si>
     <t>说明</t>
   </si>
@@ -138,10 +154,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>dim_op_goal_daily</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>dim_special_map</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -173,10 +185,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>user_flagged_d</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>ads_cn.ads_user_flagged_i_d</t>
   </si>
   <si>
@@ -184,9 +192,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>dim_cn.dim_channel_a_d_cn</t>
-  </si>
-  <si>
     <t>有现成的</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -243,31 +248,119 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>dim_cn.dim_ad_slot_config_a_d</t>
-  </si>
-  <si>
-    <t>dim_cn.dim_op_goal_a_d</t>
-  </si>
-  <si>
-    <t>dim_cn.dim_special_contentpack_a_d</t>
-  </si>
-  <si>
     <t>dim_cn.dim_special_map_a_d</t>
-  </si>
-  <si>
-    <t>验证?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>dws_cn.dws_client_game_user_map_stats_i_d</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dws_cn.dws_client_game_map_stats_i_d</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dws_cn.dws_client_game_map_place_stats_i_d</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dim_cn.dim_ad_slot_config_a_d</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dim_cn.dim_channel_a_d_cn</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dim_cn.dim_special_contentpack_a_d</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_flagged</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>验收</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dim_op_goal_d</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dim_cn.dim_op_goal_a_d</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>READY</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_id</t>
+  </si>
+  <si>
+    <t>ctype</t>
+  </si>
+  <si>
+    <t>game_cnt</t>
+  </si>
+  <si>
+    <t>game_user</t>
+  </si>
+  <si>
+    <t>game_dur</t>
+  </si>
+  <si>
+    <t>frndgame_cnt</t>
+  </si>
+  <si>
+    <t>frndgame_user</t>
+  </si>
+  <si>
+    <t>frndgame_dur</t>
+  </si>
+  <si>
+    <t>dt</t>
+  </si>
+  <si>
+    <t>DAU渗透</t>
+  </si>
+  <si>
+    <t>地图游戏时长
+(小时)</t>
+  </si>
+  <si>
+    <t>总游戏时长
+占比</t>
+  </si>
+  <si>
+    <t>人均时长
+(秒)</t>
+  </si>
+  <si>
+    <t>总内容内购
+(元)</t>
+  </si>
+  <si>
+    <t>地图内购
+(元)</t>
+  </si>
+  <si>
+    <t>广告
+(元)</t>
+  </si>
+  <si>
+    <t>广告人数渗透</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,8 +510,15 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -622,8 +722,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAD355"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8EE085"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7EDAFB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF57AC0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -750,6 +880,21 @@
       </top>
       <bottom style="thin">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F2329"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF1F2329"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1F2329"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF1F2329"/>
       </bottom>
       <diagonal/>
     </border>
@@ -882,7 +1027,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -918,6 +1063,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="41" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1294,7 +1457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D639A680-3387-4533-8FC5-EB02377F5246}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.88671875" customWidth="1"/>
@@ -1302,10 +1465,10 @@
     <col min="3" max="3" width="16.44140625" customWidth="1"/>
     <col min="4" max="6" width="8.88671875" style="10"/>
     <col min="7" max="7" width="41.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="27.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -1319,229 +1482,244 @@
         <v>4</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="9"/>
+        <v>41</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="G2" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="9"/>
+        <v>41</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="G3" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="9"/>
+        <v>41</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="G4" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="9"/>
+        <v>41</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>67</v>
+      </c>
       <c r="G6" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="11" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G10" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="11" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="11" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G14" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1550,23 +1728,23 @@
       <c r="F15" s="9"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1776,4 +1954,5391 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F40C446-9CFA-4D45-954F-4F7FCC62C1D9}">
+  <dimension ref="A1:S101"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M1" t="s">
+        <v>71</v>
+      </c>
+      <c r="N1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>75</v>
+      </c>
+      <c r="R1" t="s">
+        <v>76</v>
+      </c>
+      <c r="S1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>10000170970907</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>110</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K2">
+        <v>10000170970907</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2">
+        <v>110</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>10000242009415</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>9658</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>9020</v>
+      </c>
+      <c r="I3" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K3">
+        <v>10000242009415</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+      <c r="N3">
+        <v>8</v>
+      </c>
+      <c r="O3">
+        <v>9658</v>
+      </c>
+      <c r="P3">
+        <v>7</v>
+      </c>
+      <c r="Q3">
+        <v>5</v>
+      </c>
+      <c r="R3">
+        <v>9020</v>
+      </c>
+      <c r="S3" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>10000317348361</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>5318</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>5150</v>
+      </c>
+      <c r="I4" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K4">
+        <v>10000317348361</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>7</v>
+      </c>
+      <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4">
+        <v>5318</v>
+      </c>
+      <c r="P4">
+        <v>7</v>
+      </c>
+      <c r="Q4">
+        <v>2</v>
+      </c>
+      <c r="R4">
+        <v>5150</v>
+      </c>
+      <c r="S4" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>10000325483140</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>78</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K5">
+        <v>10000325483140</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>78</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>10000366969973</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>2244</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>2223</v>
+      </c>
+      <c r="I6" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K6">
+        <v>10000366969973</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>2244</v>
+      </c>
+      <c r="P6">
+        <v>3</v>
+      </c>
+      <c r="Q6">
+        <v>3</v>
+      </c>
+      <c r="R6">
+        <v>2223</v>
+      </c>
+      <c r="S6" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>10000422317773</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>32</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K7">
+        <v>10000422317773</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>32</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>10000446242257</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>9</v>
+      </c>
+      <c r="E8">
+        <v>20128</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="I8" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K8">
+        <v>10000446242257</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>10</v>
+      </c>
+      <c r="N8">
+        <v>9</v>
+      </c>
+      <c r="O8">
+        <v>20128</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>10000466957547</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1151</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K9">
+        <v>10000466957547</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>2</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1151</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>10000503880184</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>53</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="I10" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K10">
+        <v>10000503880184</v>
+      </c>
+      <c r="L10">
+        <v>2</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>53</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10000577176740</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>3416</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="I11" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K11">
+        <v>10000577176740</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>3416</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10000582193761</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1208</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K12">
+        <v>10000582193761</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1208</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>10000584317576</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>271</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K13">
+        <v>10000584317576</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>271</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>10000584363161</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>514</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K14">
+        <v>10000584363161</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>514</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>10000610554476</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>9</v>
+      </c>
+      <c r="D15">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>1276</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="I15" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K15">
+        <v>10000610554476</v>
+      </c>
+      <c r="L15">
+        <v>2</v>
+      </c>
+      <c r="M15">
+        <v>9</v>
+      </c>
+      <c r="N15">
+        <v>6</v>
+      </c>
+      <c r="O15">
+        <v>1276</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>10000674918456</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>82</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="I16" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K16">
+        <v>10000674918456</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>82</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>10000684159305</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>3342</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>1952</v>
+      </c>
+      <c r="I17" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K17">
+        <v>10000684159305</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>3</v>
+      </c>
+      <c r="N17">
+        <v>2</v>
+      </c>
+      <c r="O17">
+        <v>3342</v>
+      </c>
+      <c r="P17">
+        <v>2</v>
+      </c>
+      <c r="Q17">
+        <v>2</v>
+      </c>
+      <c r="R17">
+        <v>1952</v>
+      </c>
+      <c r="S17" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>10003020396145</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>41</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="I18" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K18">
+        <v>10003020396145</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>41</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>10003118537636</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>124</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="I19" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K19">
+        <v>10003118537636</v>
+      </c>
+      <c r="L19">
+        <v>2</v>
+      </c>
+      <c r="M19">
+        <v>2</v>
+      </c>
+      <c r="N19">
+        <v>2</v>
+      </c>
+      <c r="O19">
+        <v>124</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>10003207094190</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>152</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="I20" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K20">
+        <v>10003207094190</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>152</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>10003423004518</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>138</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="I21" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K21">
+        <v>10003423004518</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>138</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>10003656120618</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>778</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="I22" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K22">
+        <v>10003656120618</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <v>778</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>10003674179228</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>846</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="I23" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K23">
+        <v>10003674179228</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>846</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>10003803228249</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>92</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="I24" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K24">
+        <v>10003803228249</v>
+      </c>
+      <c r="L24">
+        <v>2</v>
+      </c>
+      <c r="M24">
+        <v>2</v>
+      </c>
+      <c r="N24">
+        <v>2</v>
+      </c>
+      <c r="O24">
+        <v>92</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>10003924887134</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>892</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="I25" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K25">
+        <v>10003924887134</v>
+      </c>
+      <c r="L25">
+        <v>2</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <v>892</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>10003927522362</v>
+      </c>
+      <c r="B26">
+        <v>2</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>606</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>584</v>
+      </c>
+      <c r="I26" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K26">
+        <v>10003927522362</v>
+      </c>
+      <c r="L26">
+        <v>2</v>
+      </c>
+      <c r="M26">
+        <v>2</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <v>606</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+      <c r="R26">
+        <v>584</v>
+      </c>
+      <c r="S26" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>10003953475204</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27">
+        <v>1134</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+      <c r="H27">
+        <v>603</v>
+      </c>
+      <c r="I27" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K27">
+        <v>10003953475204</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>4</v>
+      </c>
+      <c r="N27">
+        <v>4</v>
+      </c>
+      <c r="O27">
+        <v>1134</v>
+      </c>
+      <c r="P27">
+        <v>2</v>
+      </c>
+      <c r="Q27">
+        <v>2</v>
+      </c>
+      <c r="R27">
+        <v>603</v>
+      </c>
+      <c r="S27" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>10004067902324</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>7</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>9740</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="I28" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K28">
+        <v>10004067902324</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>7</v>
+      </c>
+      <c r="N28">
+        <v>2</v>
+      </c>
+      <c r="O28">
+        <v>9740</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>10004115284156</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>362</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="I29" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K29">
+        <v>10004115284156</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+      <c r="O29">
+        <v>362</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>10004197320905</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>899</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="I30" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K30">
+        <v>10004197320905</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30">
+        <v>899</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>10004338336757</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>140</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="I31" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K31">
+        <v>10004338336757</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="O31">
+        <v>140</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>10004438796567</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>34</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="I32" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K32">
+        <v>10004438796567</v>
+      </c>
+      <c r="L32">
+        <v>2</v>
+      </c>
+      <c r="M32">
+        <v>1</v>
+      </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
+      <c r="O32">
+        <v>34</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>10004440588924</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>260</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="I33" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K33">
+        <v>10004440588924</v>
+      </c>
+      <c r="L33">
+        <v>2</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+      <c r="N33">
+        <v>1</v>
+      </c>
+      <c r="O33">
+        <v>260</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>10004590396752</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>12</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="I34" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K34">
+        <v>10004590396752</v>
+      </c>
+      <c r="L34">
+        <v>2</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
+      <c r="O34">
+        <v>12</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>10004677910232</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>8</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="I35" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K35">
+        <v>10004677910232</v>
+      </c>
+      <c r="L35">
+        <v>2</v>
+      </c>
+      <c r="M35">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
+      <c r="O35">
+        <v>8</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>10004738027021</v>
+      </c>
+      <c r="B36">
+        <v>2</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>353</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="I36" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K36">
+        <v>10004738027021</v>
+      </c>
+      <c r="L36">
+        <v>2</v>
+      </c>
+      <c r="M36">
+        <v>2</v>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+      <c r="O36">
+        <v>353</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>10004762608595</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>44</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="I37" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K37">
+        <v>10004762608595</v>
+      </c>
+      <c r="L37">
+        <v>2</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+      <c r="O37">
+        <v>44</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>10004790344445</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38">
+        <v>17</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>2</v>
+      </c>
+      <c r="I38" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K38">
+        <v>10004790344445</v>
+      </c>
+      <c r="L38">
+        <v>1</v>
+      </c>
+      <c r="M38">
+        <v>2</v>
+      </c>
+      <c r="N38">
+        <v>2</v>
+      </c>
+      <c r="O38">
+        <v>17</v>
+      </c>
+      <c r="P38">
+        <v>1</v>
+      </c>
+      <c r="Q38">
+        <v>1</v>
+      </c>
+      <c r="R38">
+        <v>2</v>
+      </c>
+      <c r="S38" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>10004807338079</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>420</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="I39" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K39">
+        <v>10004807338079</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39">
+        <v>3</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+      <c r="O39">
+        <v>420</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>10004814294070</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>94</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="I40" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K40">
+        <v>10004814294070</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40">
+        <v>1</v>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+      <c r="O40">
+        <v>94</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>10004879330457</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41">
+        <v>406</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="I41" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K41">
+        <v>10004879330457</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>2</v>
+      </c>
+      <c r="N41">
+        <v>2</v>
+      </c>
+      <c r="O41">
+        <v>406</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>10004885766856</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>4</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42">
+        <v>2066</v>
+      </c>
+      <c r="F42">
+        <v>2</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+      <c r="H42">
+        <v>896</v>
+      </c>
+      <c r="I42" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K42">
+        <v>10004885766856</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>4</v>
+      </c>
+      <c r="N42">
+        <v>2</v>
+      </c>
+      <c r="O42">
+        <v>2066</v>
+      </c>
+      <c r="P42">
+        <v>2</v>
+      </c>
+      <c r="Q42">
+        <v>2</v>
+      </c>
+      <c r="R42">
+        <v>896</v>
+      </c>
+      <c r="S42" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>10004900261293</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>46</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="I43" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K43">
+        <v>10004900261293</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="M43">
+        <v>1</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="O43">
+        <v>46</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>10004953791750</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>9</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>3045</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="I44" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K44">
+        <v>10004953791750</v>
+      </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <v>9</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+      <c r="O44">
+        <v>3045</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>10005025010961</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>9</v>
+      </c>
+      <c r="D45">
+        <v>7</v>
+      </c>
+      <c r="E45">
+        <v>16411</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="I45" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K45">
+        <v>10005025010961</v>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45">
+        <v>9</v>
+      </c>
+      <c r="N45">
+        <v>7</v>
+      </c>
+      <c r="O45">
+        <v>16411</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>10007275799233</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+      <c r="C46">
+        <v>243</v>
+      </c>
+      <c r="D46">
+        <v>201</v>
+      </c>
+      <c r="E46">
+        <v>144212</v>
+      </c>
+      <c r="F46">
+        <v>30</v>
+      </c>
+      <c r="G46">
+        <v>21</v>
+      </c>
+      <c r="H46">
+        <v>17199</v>
+      </c>
+      <c r="I46" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K46">
+        <v>10007275799233</v>
+      </c>
+      <c r="L46">
+        <v>2</v>
+      </c>
+      <c r="M46">
+        <v>243</v>
+      </c>
+      <c r="N46">
+        <v>201</v>
+      </c>
+      <c r="O46">
+        <v>144212</v>
+      </c>
+      <c r="P46">
+        <v>30</v>
+      </c>
+      <c r="Q46">
+        <v>21</v>
+      </c>
+      <c r="R46">
+        <v>17199</v>
+      </c>
+      <c r="S46" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>10007341284654</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47">
+        <v>10</v>
+      </c>
+      <c r="D47">
+        <v>8</v>
+      </c>
+      <c r="E47">
+        <v>7803</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="I47" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K47">
+        <v>10007341284654</v>
+      </c>
+      <c r="L47">
+        <v>2</v>
+      </c>
+      <c r="M47">
+        <v>10</v>
+      </c>
+      <c r="N47">
+        <v>8</v>
+      </c>
+      <c r="O47">
+        <v>7803</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>10007346257735</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+      <c r="E48">
+        <v>39</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="I48" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K48">
+        <v>10007346257735</v>
+      </c>
+      <c r="L48">
+        <v>2</v>
+      </c>
+      <c r="M48">
+        <v>2</v>
+      </c>
+      <c r="N48">
+        <v>2</v>
+      </c>
+      <c r="O48">
+        <v>39</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>10007455814889</v>
+      </c>
+      <c r="B49">
+        <v>2</v>
+      </c>
+      <c r="C49">
+        <v>368</v>
+      </c>
+      <c r="D49">
+        <v>309</v>
+      </c>
+      <c r="E49">
+        <v>349500</v>
+      </c>
+      <c r="F49">
+        <v>24</v>
+      </c>
+      <c r="G49">
+        <v>20</v>
+      </c>
+      <c r="H49">
+        <v>53615</v>
+      </c>
+      <c r="I49" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K49">
+        <v>10007455814889</v>
+      </c>
+      <c r="L49">
+        <v>2</v>
+      </c>
+      <c r="M49">
+        <v>368</v>
+      </c>
+      <c r="N49">
+        <v>309</v>
+      </c>
+      <c r="O49">
+        <v>349500</v>
+      </c>
+      <c r="P49">
+        <v>24</v>
+      </c>
+      <c r="Q49">
+        <v>20</v>
+      </c>
+      <c r="R49">
+        <v>53615</v>
+      </c>
+      <c r="S49" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>10007660090448</v>
+      </c>
+      <c r="B50">
+        <v>2</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>51</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="I50" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K50">
+        <v>10007660090448</v>
+      </c>
+      <c r="L50">
+        <v>2</v>
+      </c>
+      <c r="M50">
+        <v>1</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+      <c r="O50">
+        <v>51</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>10008010305948</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51">
+        <v>2892</v>
+      </c>
+      <c r="F51">
+        <v>3</v>
+      </c>
+      <c r="G51">
+        <v>3</v>
+      </c>
+      <c r="H51">
+        <v>2847</v>
+      </c>
+      <c r="I51" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K51">
+        <v>10008010305948</v>
+      </c>
+      <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="M51">
+        <v>3</v>
+      </c>
+      <c r="N51">
+        <v>3</v>
+      </c>
+      <c r="O51">
+        <v>2892</v>
+      </c>
+      <c r="P51">
+        <v>3</v>
+      </c>
+      <c r="Q51">
+        <v>3</v>
+      </c>
+      <c r="R51">
+        <v>2847</v>
+      </c>
+      <c r="S51" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>10008210610112</v>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52">
+        <v>65</v>
+      </c>
+      <c r="D52">
+        <v>46</v>
+      </c>
+      <c r="E52">
+        <v>26378</v>
+      </c>
+      <c r="F52">
+        <v>34</v>
+      </c>
+      <c r="G52">
+        <v>24</v>
+      </c>
+      <c r="H52">
+        <v>22637</v>
+      </c>
+      <c r="I52" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K52">
+        <v>10008210610112</v>
+      </c>
+      <c r="L52">
+        <v>2</v>
+      </c>
+      <c r="M52">
+        <v>65</v>
+      </c>
+      <c r="N52">
+        <v>46</v>
+      </c>
+      <c r="O52">
+        <v>26378</v>
+      </c>
+      <c r="P52">
+        <v>34</v>
+      </c>
+      <c r="Q52">
+        <v>24</v>
+      </c>
+      <c r="R52">
+        <v>22637</v>
+      </c>
+      <c r="S52" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>10008350214718</v>
+      </c>
+      <c r="B53">
+        <v>2</v>
+      </c>
+      <c r="C53">
+        <v>272</v>
+      </c>
+      <c r="D53">
+        <v>197</v>
+      </c>
+      <c r="E53">
+        <v>83041</v>
+      </c>
+      <c r="F53">
+        <v>37</v>
+      </c>
+      <c r="G53">
+        <v>29</v>
+      </c>
+      <c r="H53">
+        <v>8393</v>
+      </c>
+      <c r="I53" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K53">
+        <v>10008350214718</v>
+      </c>
+      <c r="L53">
+        <v>2</v>
+      </c>
+      <c r="M53">
+        <v>272</v>
+      </c>
+      <c r="N53">
+        <v>197</v>
+      </c>
+      <c r="O53">
+        <v>83041</v>
+      </c>
+      <c r="P53">
+        <v>37</v>
+      </c>
+      <c r="Q53">
+        <v>29</v>
+      </c>
+      <c r="R53">
+        <v>8393</v>
+      </c>
+      <c r="S53" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>10008407013623</v>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>903</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="I54" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K54">
+        <v>10008407013623</v>
+      </c>
+      <c r="L54">
+        <v>2</v>
+      </c>
+      <c r="M54">
+        <v>1</v>
+      </c>
+      <c r="N54">
+        <v>1</v>
+      </c>
+      <c r="O54">
+        <v>903</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>10008573582613</v>
+      </c>
+      <c r="B55">
+        <v>2</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>93</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="I55" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K55">
+        <v>10008573582613</v>
+      </c>
+      <c r="L55">
+        <v>2</v>
+      </c>
+      <c r="M55">
+        <v>1</v>
+      </c>
+      <c r="N55">
+        <v>1</v>
+      </c>
+      <c r="O55">
+        <v>93</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>10008695100701</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56">
+        <v>15</v>
+      </c>
+      <c r="D56">
+        <v>10</v>
+      </c>
+      <c r="E56">
+        <v>20036</v>
+      </c>
+      <c r="F56">
+        <v>2</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
+      </c>
+      <c r="H56">
+        <v>3564</v>
+      </c>
+      <c r="I56" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K56">
+        <v>10008695100701</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56">
+        <v>15</v>
+      </c>
+      <c r="N56">
+        <v>10</v>
+      </c>
+      <c r="O56">
+        <v>20036</v>
+      </c>
+      <c r="P56">
+        <v>2</v>
+      </c>
+      <c r="Q56">
+        <v>2</v>
+      </c>
+      <c r="R56">
+        <v>3564</v>
+      </c>
+      <c r="S56" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>10008701457002</v>
+      </c>
+      <c r="B57">
+        <v>2</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>228</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="I57" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K57">
+        <v>10008701457002</v>
+      </c>
+      <c r="L57">
+        <v>2</v>
+      </c>
+      <c r="M57">
+        <v>1</v>
+      </c>
+      <c r="N57">
+        <v>1</v>
+      </c>
+      <c r="O57">
+        <v>228</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>10008708493330</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>358</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="I58" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K58">
+        <v>10008708493330</v>
+      </c>
+      <c r="L58">
+        <v>1</v>
+      </c>
+      <c r="M58">
+        <v>1</v>
+      </c>
+      <c r="N58">
+        <v>1</v>
+      </c>
+      <c r="O58">
+        <v>358</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>10008710575267</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>473</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="I59" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K59">
+        <v>10008710575267</v>
+      </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
+      <c r="M59">
+        <v>1</v>
+      </c>
+      <c r="N59">
+        <v>1</v>
+      </c>
+      <c r="O59">
+        <v>473</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>10008928053616</v>
+      </c>
+      <c r="B60">
+        <v>2</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+      <c r="E60">
+        <v>133</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="I60" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K60">
+        <v>10008928053616</v>
+      </c>
+      <c r="L60">
+        <v>2</v>
+      </c>
+      <c r="M60">
+        <v>1</v>
+      </c>
+      <c r="N60">
+        <v>1</v>
+      </c>
+      <c r="O60">
+        <v>133</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>10008973589432</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61">
+        <v>9</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>11015</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="I61" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K61">
+        <v>10008973589432</v>
+      </c>
+      <c r="L61">
+        <v>1</v>
+      </c>
+      <c r="M61">
+        <v>9</v>
+      </c>
+      <c r="N61">
+        <v>1</v>
+      </c>
+      <c r="O61">
+        <v>11015</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>10008979622292</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+      <c r="E62">
+        <v>253</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="I62" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K62">
+        <v>10008979622292</v>
+      </c>
+      <c r="L62">
+        <v>2</v>
+      </c>
+      <c r="M62">
+        <v>2</v>
+      </c>
+      <c r="N62">
+        <v>2</v>
+      </c>
+      <c r="O62">
+        <v>253</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>10008987071106</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>131</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="I63" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K63">
+        <v>10008987071106</v>
+      </c>
+      <c r="L63">
+        <v>2</v>
+      </c>
+      <c r="M63">
+        <v>1</v>
+      </c>
+      <c r="N63">
+        <v>1</v>
+      </c>
+      <c r="O63">
+        <v>131</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>10008992463876</v>
+      </c>
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+      <c r="D64">
+        <v>2</v>
+      </c>
+      <c r="E64">
+        <v>267</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="I64" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K64">
+        <v>10008992463876</v>
+      </c>
+      <c r="L64">
+        <v>2</v>
+      </c>
+      <c r="M64">
+        <v>2</v>
+      </c>
+      <c r="N64">
+        <v>2</v>
+      </c>
+      <c r="O64">
+        <v>267</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>10009040029322</v>
+      </c>
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65">
+        <v>71</v>
+      </c>
+      <c r="D65">
+        <v>62</v>
+      </c>
+      <c r="E65">
+        <v>9457</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="I65" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K65">
+        <v>10009040029322</v>
+      </c>
+      <c r="L65">
+        <v>2</v>
+      </c>
+      <c r="M65">
+        <v>71</v>
+      </c>
+      <c r="N65">
+        <v>62</v>
+      </c>
+      <c r="O65">
+        <v>9457</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>10009071459480</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
+      </c>
+      <c r="C66">
+        <v>4</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66">
+        <v>2535</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="I66" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K66">
+        <v>10009071459480</v>
+      </c>
+      <c r="L66">
+        <v>2</v>
+      </c>
+      <c r="M66">
+        <v>4</v>
+      </c>
+      <c r="N66">
+        <v>1</v>
+      </c>
+      <c r="O66">
+        <v>2535</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>10009083283185</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
+      <c r="C67">
+        <v>29</v>
+      </c>
+      <c r="D67">
+        <v>13</v>
+      </c>
+      <c r="E67">
+        <v>2926</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="I67" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K67">
+        <v>10009083283185</v>
+      </c>
+      <c r="L67">
+        <v>2</v>
+      </c>
+      <c r="M67">
+        <v>29</v>
+      </c>
+      <c r="N67">
+        <v>13</v>
+      </c>
+      <c r="O67">
+        <v>2926</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>10009084557497</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="I68" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K68">
+        <v>10009084557497</v>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+      <c r="M68">
+        <v>1</v>
+      </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
+      <c r="O68">
+        <v>2</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>10009108916003</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69">
+        <v>32</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="I69" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K69">
+        <v>10009108916003</v>
+      </c>
+      <c r="L69">
+        <v>2</v>
+      </c>
+      <c r="M69">
+        <v>1</v>
+      </c>
+      <c r="N69">
+        <v>1</v>
+      </c>
+      <c r="O69">
+        <v>32</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>10009118618740</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>34</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="I70" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K70">
+        <v>10009118618740</v>
+      </c>
+      <c r="L70">
+        <v>2</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+      <c r="N70">
+        <v>1</v>
+      </c>
+      <c r="O70">
+        <v>34</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>10009139298115</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
+      </c>
+      <c r="C71">
+        <v>2</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>45</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="I71" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K71">
+        <v>10009139298115</v>
+      </c>
+      <c r="L71">
+        <v>2</v>
+      </c>
+      <c r="M71">
+        <v>2</v>
+      </c>
+      <c r="N71">
+        <v>1</v>
+      </c>
+      <c r="O71">
+        <v>45</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>10009149015299</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72">
+        <v>812</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="I72" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K72">
+        <v>10009149015299</v>
+      </c>
+      <c r="L72">
+        <v>1</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="N72">
+        <v>1</v>
+      </c>
+      <c r="O72">
+        <v>812</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>10009151534502</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73">
+        <v>2</v>
+      </c>
+      <c r="D73">
+        <v>2</v>
+      </c>
+      <c r="E73">
+        <v>136</v>
+      </c>
+      <c r="F73">
+        <v>2</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+      <c r="H73">
+        <v>115</v>
+      </c>
+      <c r="I73" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K73">
+        <v>10009151534502</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+      <c r="M73">
+        <v>2</v>
+      </c>
+      <c r="N73">
+        <v>2</v>
+      </c>
+      <c r="O73">
+        <v>136</v>
+      </c>
+      <c r="P73">
+        <v>2</v>
+      </c>
+      <c r="Q73">
+        <v>2</v>
+      </c>
+      <c r="R73">
+        <v>115</v>
+      </c>
+      <c r="S73" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>10009153948206</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74">
+        <v>5</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74">
+        <v>4615</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="I74" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K74">
+        <v>10009153948206</v>
+      </c>
+      <c r="L74">
+        <v>1</v>
+      </c>
+      <c r="M74">
+        <v>5</v>
+      </c>
+      <c r="N74">
+        <v>1</v>
+      </c>
+      <c r="O74">
+        <v>4615</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>10009180276576</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75">
+        <v>20</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="I75" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K75">
+        <v>10009180276576</v>
+      </c>
+      <c r="L75">
+        <v>2</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75">
+        <v>1</v>
+      </c>
+      <c r="O75">
+        <v>20</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>10009312904928</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>3690</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="I76" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K76">
+        <v>10009312904928</v>
+      </c>
+      <c r="L76">
+        <v>1</v>
+      </c>
+      <c r="M76">
+        <v>3</v>
+      </c>
+      <c r="N76">
+        <v>1</v>
+      </c>
+      <c r="O76">
+        <v>3690</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+      <c r="S76" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>10011711412104</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77">
+        <v>33</v>
+      </c>
+      <c r="D77">
+        <v>32</v>
+      </c>
+      <c r="E77">
+        <v>12526</v>
+      </c>
+      <c r="F77">
+        <v>2</v>
+      </c>
+      <c r="G77">
+        <v>2</v>
+      </c>
+      <c r="H77">
+        <v>106</v>
+      </c>
+      <c r="I77" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K77">
+        <v>10011711412104</v>
+      </c>
+      <c r="L77">
+        <v>1</v>
+      </c>
+      <c r="M77">
+        <v>33</v>
+      </c>
+      <c r="N77">
+        <v>32</v>
+      </c>
+      <c r="O77">
+        <v>12526</v>
+      </c>
+      <c r="P77">
+        <v>2</v>
+      </c>
+      <c r="Q77">
+        <v>2</v>
+      </c>
+      <c r="R77">
+        <v>106</v>
+      </c>
+      <c r="S77" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>10011911228716</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78">
+        <v>954</v>
+      </c>
+      <c r="D78">
+        <v>785</v>
+      </c>
+      <c r="E78">
+        <v>513531</v>
+      </c>
+      <c r="F78">
+        <v>194</v>
+      </c>
+      <c r="G78">
+        <v>172</v>
+      </c>
+      <c r="H78">
+        <v>167710</v>
+      </c>
+      <c r="I78" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K78">
+        <v>10011911228716</v>
+      </c>
+      <c r="L78">
+        <v>2</v>
+      </c>
+      <c r="M78">
+        <v>954</v>
+      </c>
+      <c r="N78">
+        <v>785</v>
+      </c>
+      <c r="O78">
+        <v>513531</v>
+      </c>
+      <c r="P78">
+        <v>194</v>
+      </c>
+      <c r="Q78">
+        <v>172</v>
+      </c>
+      <c r="R78">
+        <v>167710</v>
+      </c>
+      <c r="S78" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>10011966446160</v>
+      </c>
+      <c r="B79">
+        <v>1</v>
+      </c>
+      <c r="C79">
+        <v>2</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79">
+        <v>4142</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="I79" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K79">
+        <v>10011966446160</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="M79">
+        <v>2</v>
+      </c>
+      <c r="N79">
+        <v>1</v>
+      </c>
+      <c r="O79">
+        <v>4142</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+      <c r="S79" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>10012229799591</v>
+      </c>
+      <c r="B80">
+        <v>2</v>
+      </c>
+      <c r="C80">
+        <v>59</v>
+      </c>
+      <c r="D80">
+        <v>14</v>
+      </c>
+      <c r="E80">
+        <v>20026</v>
+      </c>
+      <c r="F80">
+        <v>17</v>
+      </c>
+      <c r="G80">
+        <v>7</v>
+      </c>
+      <c r="H80">
+        <v>4757</v>
+      </c>
+      <c r="I80" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K80">
+        <v>10012229799591</v>
+      </c>
+      <c r="L80">
+        <v>2</v>
+      </c>
+      <c r="M80">
+        <v>59</v>
+      </c>
+      <c r="N80">
+        <v>14</v>
+      </c>
+      <c r="O80">
+        <v>20026</v>
+      </c>
+      <c r="P80">
+        <v>17</v>
+      </c>
+      <c r="Q80">
+        <v>7</v>
+      </c>
+      <c r="R80">
+        <v>4757</v>
+      </c>
+      <c r="S80" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>10012379456204</v>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81">
+        <v>33</v>
+      </c>
+      <c r="D81">
+        <v>2</v>
+      </c>
+      <c r="E81">
+        <v>48672</v>
+      </c>
+      <c r="F81">
+        <v>25</v>
+      </c>
+      <c r="G81">
+        <v>2</v>
+      </c>
+      <c r="H81">
+        <v>33985</v>
+      </c>
+      <c r="I81" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K81">
+        <v>10012379456204</v>
+      </c>
+      <c r="L81">
+        <v>1</v>
+      </c>
+      <c r="M81">
+        <v>33</v>
+      </c>
+      <c r="N81">
+        <v>2</v>
+      </c>
+      <c r="O81">
+        <v>48672</v>
+      </c>
+      <c r="P81">
+        <v>25</v>
+      </c>
+      <c r="Q81">
+        <v>2</v>
+      </c>
+      <c r="R81">
+        <v>33985</v>
+      </c>
+      <c r="S81" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>10012388184862</v>
+      </c>
+      <c r="B82">
+        <v>2</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82">
+        <v>36</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="I82" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K82">
+        <v>10012388184862</v>
+      </c>
+      <c r="L82">
+        <v>2</v>
+      </c>
+      <c r="M82">
+        <v>1</v>
+      </c>
+      <c r="N82">
+        <v>1</v>
+      </c>
+      <c r="O82">
+        <v>36</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+      <c r="S82" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>10012470575875</v>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83">
+        <v>98</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="I83" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K83">
+        <v>10012470575875</v>
+      </c>
+      <c r="L83">
+        <v>1</v>
+      </c>
+      <c r="M83">
+        <v>1</v>
+      </c>
+      <c r="N83">
+        <v>1</v>
+      </c>
+      <c r="O83">
+        <v>98</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="R83">
+        <v>0</v>
+      </c>
+      <c r="S83" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>10012480133388</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84">
+        <v>3</v>
+      </c>
+      <c r="D84">
+        <v>2</v>
+      </c>
+      <c r="E84">
+        <v>698</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="I84" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K84">
+        <v>10012480133388</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84">
+        <v>3</v>
+      </c>
+      <c r="N84">
+        <v>2</v>
+      </c>
+      <c r="O84">
+        <v>698</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="R84">
+        <v>0</v>
+      </c>
+      <c r="S84" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>10012598233240</v>
+      </c>
+      <c r="B85">
+        <v>2</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <v>104</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="I85" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K85">
+        <v>10012598233240</v>
+      </c>
+      <c r="L85">
+        <v>2</v>
+      </c>
+      <c r="M85">
+        <v>1</v>
+      </c>
+      <c r="N85">
+        <v>1</v>
+      </c>
+      <c r="O85">
+        <v>104</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>0</v>
+      </c>
+      <c r="R85">
+        <v>0</v>
+      </c>
+      <c r="S85" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>10012634242769</v>
+      </c>
+      <c r="B86">
+        <v>2</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86">
+        <v>223</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="I86" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K86">
+        <v>10012634242769</v>
+      </c>
+      <c r="L86">
+        <v>2</v>
+      </c>
+      <c r="M86">
+        <v>1</v>
+      </c>
+      <c r="N86">
+        <v>1</v>
+      </c>
+      <c r="O86">
+        <v>223</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="R86">
+        <v>0</v>
+      </c>
+      <c r="S86" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>10012634346999</v>
+      </c>
+      <c r="B87">
+        <v>2</v>
+      </c>
+      <c r="C87">
+        <v>4</v>
+      </c>
+      <c r="D87">
+        <v>3</v>
+      </c>
+      <c r="E87">
+        <v>383</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="I87" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K87">
+        <v>10012634346999</v>
+      </c>
+      <c r="L87">
+        <v>2</v>
+      </c>
+      <c r="M87">
+        <v>4</v>
+      </c>
+      <c r="N87">
+        <v>3</v>
+      </c>
+      <c r="O87">
+        <v>383</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>0</v>
+      </c>
+      <c r="R87">
+        <v>0</v>
+      </c>
+      <c r="S87" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>10012975304822</v>
+      </c>
+      <c r="B88">
+        <v>2</v>
+      </c>
+      <c r="C88">
+        <v>2</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88">
+        <v>243</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="I88" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K88">
+        <v>10012975304822</v>
+      </c>
+      <c r="L88">
+        <v>2</v>
+      </c>
+      <c r="M88">
+        <v>2</v>
+      </c>
+      <c r="N88">
+        <v>1</v>
+      </c>
+      <c r="O88">
+        <v>243</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>0</v>
+      </c>
+      <c r="R88">
+        <v>0</v>
+      </c>
+      <c r="S88" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>10013092319327</v>
+      </c>
+      <c r="B89">
+        <v>2</v>
+      </c>
+      <c r="C89">
+        <v>3</v>
+      </c>
+      <c r="D89">
+        <v>2</v>
+      </c>
+      <c r="E89">
+        <v>855</v>
+      </c>
+      <c r="F89">
+        <v>3</v>
+      </c>
+      <c r="G89">
+        <v>2</v>
+      </c>
+      <c r="H89">
+        <v>781</v>
+      </c>
+      <c r="I89" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K89">
+        <v>10013092319327</v>
+      </c>
+      <c r="L89">
+        <v>2</v>
+      </c>
+      <c r="M89">
+        <v>3</v>
+      </c>
+      <c r="N89">
+        <v>2</v>
+      </c>
+      <c r="O89">
+        <v>855</v>
+      </c>
+      <c r="P89">
+        <v>3</v>
+      </c>
+      <c r="Q89">
+        <v>2</v>
+      </c>
+      <c r="R89">
+        <v>781</v>
+      </c>
+      <c r="S89" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>10013092562349</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90">
+        <v>10</v>
+      </c>
+      <c r="D90">
+        <v>9</v>
+      </c>
+      <c r="E90">
+        <v>1729</v>
+      </c>
+      <c r="F90">
+        <v>4</v>
+      </c>
+      <c r="G90">
+        <v>4</v>
+      </c>
+      <c r="H90">
+        <v>832</v>
+      </c>
+      <c r="I90" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K90">
+        <v>10013092562349</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="M90">
+        <v>10</v>
+      </c>
+      <c r="N90">
+        <v>9</v>
+      </c>
+      <c r="O90">
+        <v>1729</v>
+      </c>
+      <c r="P90">
+        <v>4</v>
+      </c>
+      <c r="Q90">
+        <v>4</v>
+      </c>
+      <c r="R90">
+        <v>832</v>
+      </c>
+      <c r="S90" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>10013165832537</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>244</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="I91" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K91">
+        <v>10013165832537</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91">
+        <v>1</v>
+      </c>
+      <c r="N91">
+        <v>1</v>
+      </c>
+      <c r="O91">
+        <v>244</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>0</v>
+      </c>
+      <c r="R91">
+        <v>0</v>
+      </c>
+      <c r="S91" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>10013245715783</v>
+      </c>
+      <c r="B92">
+        <v>2</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>64</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="I92" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K92">
+        <v>10013245715783</v>
+      </c>
+      <c r="L92">
+        <v>2</v>
+      </c>
+      <c r="M92">
+        <v>1</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="O92">
+        <v>64</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>0</v>
+      </c>
+      <c r="R92">
+        <v>0</v>
+      </c>
+      <c r="S92" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>10013252747058</v>
+      </c>
+      <c r="B93">
+        <v>2</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93">
+        <v>63</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="I93" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K93">
+        <v>10013252747058</v>
+      </c>
+      <c r="L93">
+        <v>2</v>
+      </c>
+      <c r="M93">
+        <v>1</v>
+      </c>
+      <c r="N93">
+        <v>1</v>
+      </c>
+      <c r="O93">
+        <v>63</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>0</v>
+      </c>
+      <c r="R93">
+        <v>0</v>
+      </c>
+      <c r="S93" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>10013273425064</v>
+      </c>
+      <c r="B94">
+        <v>1</v>
+      </c>
+      <c r="C94">
+        <v>3</v>
+      </c>
+      <c r="D94">
+        <v>2</v>
+      </c>
+      <c r="E94">
+        <v>222</v>
+      </c>
+      <c r="F94">
+        <v>2</v>
+      </c>
+      <c r="G94">
+        <v>2</v>
+      </c>
+      <c r="H94">
+        <v>204</v>
+      </c>
+      <c r="I94" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K94">
+        <v>10013273425064</v>
+      </c>
+      <c r="L94">
+        <v>1</v>
+      </c>
+      <c r="M94">
+        <v>3</v>
+      </c>
+      <c r="N94">
+        <v>2</v>
+      </c>
+      <c r="O94">
+        <v>222</v>
+      </c>
+      <c r="P94">
+        <v>2</v>
+      </c>
+      <c r="Q94">
+        <v>2</v>
+      </c>
+      <c r="R94">
+        <v>204</v>
+      </c>
+      <c r="S94" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>10013352148232</v>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95">
+        <v>3</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>1580</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="I95" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K95">
+        <v>10013352148232</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="M95">
+        <v>3</v>
+      </c>
+      <c r="N95">
+        <v>1</v>
+      </c>
+      <c r="O95">
+        <v>1580</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>0</v>
+      </c>
+      <c r="R95">
+        <v>0</v>
+      </c>
+      <c r="S95" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>10013551360375</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96">
+        <v>4</v>
+      </c>
+      <c r="D96">
+        <v>3</v>
+      </c>
+      <c r="E96">
+        <v>897</v>
+      </c>
+      <c r="F96">
+        <v>3</v>
+      </c>
+      <c r="G96">
+        <v>3</v>
+      </c>
+      <c r="H96">
+        <v>718</v>
+      </c>
+      <c r="I96" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K96">
+        <v>10013551360375</v>
+      </c>
+      <c r="L96">
+        <v>1</v>
+      </c>
+      <c r="M96">
+        <v>4</v>
+      </c>
+      <c r="N96">
+        <v>3</v>
+      </c>
+      <c r="O96">
+        <v>897</v>
+      </c>
+      <c r="P96">
+        <v>3</v>
+      </c>
+      <c r="Q96">
+        <v>3</v>
+      </c>
+      <c r="R96">
+        <v>718</v>
+      </c>
+      <c r="S96" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>10016170150673</v>
+      </c>
+      <c r="B97">
+        <v>2</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>29</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="I97" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K97">
+        <v>10016170150673</v>
+      </c>
+      <c r="L97">
+        <v>2</v>
+      </c>
+      <c r="M97">
+        <v>1</v>
+      </c>
+      <c r="N97">
+        <v>1</v>
+      </c>
+      <c r="O97">
+        <v>29</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>0</v>
+      </c>
+      <c r="R97">
+        <v>0</v>
+      </c>
+      <c r="S97" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>10016499975800</v>
+      </c>
+      <c r="B98">
+        <v>2</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98">
+        <v>231</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="I98" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K98">
+        <v>10016499975800</v>
+      </c>
+      <c r="L98">
+        <v>2</v>
+      </c>
+      <c r="M98">
+        <v>2</v>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+      <c r="O98">
+        <v>231</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>0</v>
+      </c>
+      <c r="R98">
+        <v>0</v>
+      </c>
+      <c r="S98" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>10016622962802</v>
+      </c>
+      <c r="B99">
+        <v>2</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99">
+        <v>2</v>
+      </c>
+      <c r="E99">
+        <v>2804</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99">
+        <v>9</v>
+      </c>
+      <c r="I99" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K99">
+        <v>10016622962802</v>
+      </c>
+      <c r="L99">
+        <v>2</v>
+      </c>
+      <c r="M99">
+        <v>2</v>
+      </c>
+      <c r="N99">
+        <v>2</v>
+      </c>
+      <c r="O99">
+        <v>2804</v>
+      </c>
+      <c r="P99">
+        <v>1</v>
+      </c>
+      <c r="Q99">
+        <v>1</v>
+      </c>
+      <c r="R99">
+        <v>9</v>
+      </c>
+      <c r="S99" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>10016634698177</v>
+      </c>
+      <c r="B100">
+        <v>2</v>
+      </c>
+      <c r="C100">
+        <v>2</v>
+      </c>
+      <c r="D100">
+        <v>2</v>
+      </c>
+      <c r="E100">
+        <v>363</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="I100" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K100">
+        <v>10016634698177</v>
+      </c>
+      <c r="L100">
+        <v>2</v>
+      </c>
+      <c r="M100">
+        <v>2</v>
+      </c>
+      <c r="N100">
+        <v>2</v>
+      </c>
+      <c r="O100">
+        <v>363</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
+        <v>0</v>
+      </c>
+      <c r="R100">
+        <v>0</v>
+      </c>
+      <c r="S100" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>10016696078839</v>
+      </c>
+      <c r="B101">
+        <v>2</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101">
+        <v>132</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="I101" s="13">
+        <v>46054</v>
+      </c>
+      <c r="K101">
+        <v>10016696078839</v>
+      </c>
+      <c r="L101">
+        <v>2</v>
+      </c>
+      <c r="M101">
+        <v>1</v>
+      </c>
+      <c r="N101">
+        <v>1</v>
+      </c>
+      <c r="O101">
+        <v>132</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>0</v>
+      </c>
+      <c r="R101">
+        <v>0</v>
+      </c>
+      <c r="S101" s="13">
+        <v>46054</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F06E6673-E929-428E-8021-D8EA185C470D}">
+  <dimension ref="A1:S24"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="O1" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="S1" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{074AEFD0-9227-45C1-9B80-1D94C2B374B7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>